--- a/data/reports/report-2026-07-31.xlsx
+++ b/data/reports/report-2026-07-31.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="シンプル判定" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="商品別" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="商品別（4期間）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ネクストアクション" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="全体サマリー" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="一覧" sheetId="5" state="visible" r:id="rId5"/>
@@ -19526,202 +19526,1616 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="7" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="7" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="62" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>商品別（7日=7/24-30 / 3日=7/28-30 / 前日=7/30 / 30日=7/01-30。すべてShopify・Metaの実測）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>7日売上</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>7日原価</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>7日広告費</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>7日利益</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>7日利益率</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>原価率</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>広告費率</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>3日売上</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>3日原価</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>3日広告費</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>3日利益</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>3日利益率</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>前日売上</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>前日原価</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>前日広告費</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>前日利益</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>前日利益率</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>30日利益</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>MER(7日)</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>分岐</t>
-        </is>
-      </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>7日MER</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>分岐MER</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>目標MER</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>余裕</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
-        <is>
-          <t>増分MER</t>
-        </is>
-      </c>
-      <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>CVR(7日)</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
-        <is>
-          <t>CVR順位</t>
-        </is>
-      </c>
-      <c r="AA1" s="4" t="inlineStr">
-        <is>
-          <t>残シーズン(週)</t>
-        </is>
-      </c>
-      <c r="AB1" s="4" t="inlineStr">
-        <is>
-          <t>値引(7日)</t>
-        </is>
-      </c>
-      <c r="AC1" s="4" t="inlineStr">
-        <is>
-          <t>返品(7日)</t>
-        </is>
-      </c>
-      <c r="AD1" s="4" t="inlineStr">
-        <is>
-          <t>現日予算(円)</t>
-        </is>
-      </c>
-      <c r="AE1" s="4" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="AF1" s="4" t="inlineStr">
-        <is>
-          <t>推奨アクション</t>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>7日販売数</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>前日販売数</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>現日予算</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>4WAY</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>1592355</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>576090</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>632802</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>383463</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>653625</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>153046</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>201192</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>40945</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>2351824</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O4" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P4" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q4" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>333</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>形状記憶日傘</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>1244004</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>336413</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>410143</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>497448</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>483807</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>173890</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>164340</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>59184</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>2042339</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P5" s="16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q5" s="16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R5" s="21" t="n">
+        <v>257</v>
+      </c>
+      <c r="S5" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="T5" s="17" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>害虫ブロッカー</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>1236984</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>296514</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>548519</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>391951</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>452128</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>115304</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>144673</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>44507</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>2837787</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q6" s="13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>342</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>ナノガラス脱毛パッド</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>1074799</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>205905</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>457981</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>410913</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>469640</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>172459</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>179100</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>73271</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>1852704</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R7" s="21" t="n">
+        <v>274</v>
+      </c>
+      <c r="S7" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>接触冷感UVパーカー</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>681177</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>250950</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>230164</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>200063</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>276013</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>78627</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>101888</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>29311</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>724717</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q8" s="13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="T8" s="10" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>卓上冷感クーラー</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>531024</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>181636</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>224682</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>124706</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.2348</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>182988</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>33128</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>53820</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>6749</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>513056</v>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P9" s="16" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R9" s="21" t="n">
+        <v>91</v>
+      </c>
+      <c r="S9" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>完全遮光・形状記憶</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>528876</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>142681</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>261100</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>125095</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>218124</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>57856</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>79680</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>23555</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>822798</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>5WAY腰掛けファン</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>410850</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>162624</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>97953</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>150273</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>228084</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>89604</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>85407</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>36282</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>261577</v>
+      </c>
+      <c r="N11" s="16" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P11" s="16" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q11" s="16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R11" s="21" t="n">
+        <v>88</v>
+      </c>
+      <c r="S11" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ムダ毛シェーバー</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>332584</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>142698</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>88686</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>101200</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>167520</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>64457</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>48860</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>17060</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>141110</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>偏光・調光サングラス</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>256113</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>58938</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>151676</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>45499</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>100097</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>11121</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>35024</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>4396</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>482585</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R13" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="S13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>接触冷感UVアームカバー</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>253128</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>50960</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>122774</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>79394</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>124176</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>45243</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>41392</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>18921</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>378477</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>3WAYサーキュレーター</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>239200</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>104370</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>111566</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>23264</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>113620</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>16540</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>44252</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>7195</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>203261</v>
+      </c>
+      <c r="N15" s="16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O15" s="16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q15" s="16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R15" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="S15" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>瞬間冷感ポンチョ</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>230442</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>61194</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>91104</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>78144</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>84376</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>22453</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>15124</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>-1753</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>-0.1159</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>158629</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>UV歯ブラシ除菌器</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>167028</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>61560</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>67835</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>37633</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>0.2253</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>35920</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>-7084</v>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>-0.1972</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>8980</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>-5361</v>
+      </c>
+      <c r="L17" s="23" t="n">
+        <v>-0.597</v>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>195589</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Q17" s="16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R17" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="S17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="17" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>携帯電動シェーバー</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>144420</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>50547</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>77417</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>16456</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>69720</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>11912</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>24900</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>6843</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>158874</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>健康サンダル</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>133962</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>32536</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>91899</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>9527</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>0.0711</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>-7663</v>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>-0.1923</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>14940</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>-1927</v>
+      </c>
+      <c r="L19" s="23" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>226094</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q19" s="16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="R19" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="S19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>バランスケアスリッパ</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>71712</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>19560</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>34645</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>17507</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0.2441</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>13944</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>-4543</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>-0.3258</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>8964</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>59947</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>壁掛けディスペンサー</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>64604</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>23092</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>51848</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>-10336</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>19940</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>-4438</v>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>-0.2226</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>6980</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>-1773</v>
+      </c>
+      <c r="L21" s="23" t="n">
+        <v>-0.254</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <v>-206</v>
+      </c>
+      <c r="N21" s="16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O21" s="16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P21" s="16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q21" s="24" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="R21" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>湯上がりガーゼワンピース</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>31993</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>11808</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>15925</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>4260</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>15249</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>9345</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>0.6128</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>15249</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>9345</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0.6128</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>35648</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>優先配送</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>30552</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>30552</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>12328</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>12328</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>6968</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>6968</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>121672</v>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R23" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="S23" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>瞬間冷却ハンディファン</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>17940</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>6159</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>11781</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>11960</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>7854</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="10" t="n">
+        <v>67098</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P24" s="13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>カタログ全部（テスト）※全商品横断</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>204317</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>検算3本すべて通過: Σ商品売上=全店直接取得の売上（4期間とも差0円）／商品別広告費+カタログ=Metaアカウント消化（同）／原価は販売数(gross÷売価)ベースで返品を引かない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>ナノガラス脱毛パッド・壁掛けディスペンサーはバリアント別の実数量で原価を加重（4期間それぞれShopifyから実測）。ムダ毛シェーバーは7/27の値上げで売価2種のためnet_items_soldを販売数に代用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>カタログ全部（テスト）はShopify側で商品に紐づかないため売上・利益を分解できない。この行を含めると広告費列の合計＝Metaアカウント消化額と一致する。</t>
         </is>
       </c>
     </row>
